--- a/prisma/prisma-counts.xlsx
+++ b/prisma/prisma-counts.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Excl. reasons: wrong focus (~8); wrong outcome (~4); wrong setting (~3); narrative only (~3); duplicate of retained (~2); not retrievable (2) + 2 additional</t>
+          <t>Excl. reasons: wrong outcome (E2, n=9); insufficient methodology (E4, n=6); wrong setting (E3, n=4); duplicate/better source retained (E5, n=4); wrong focus (E1, n=1). See Supplementary File S2 for full list.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>17 sources: 6 systematic/umbrella reviews; 4 scoping/narrative reviews; 4 government/audit reports; 3 policy/framework/theory analyses</t>
+          <t>17 sources: 4 systematic/umbrella reviews; 3 scoping/narrative reviews; 4 government/audit reports; 6 policy/regulatory/framework analyses</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C26" s="17" t="n"/>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Holmes, Kruse, Fennelly, Aguirre, Bitar + 1 additional</t>
+          <t>Eden, Kruse, Fennelly, Torab-Miandoab</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
         </is>
       </c>
       <c r="B27" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" s="17" t="n"/>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Aguirre scoping, Adams qualitative case + 2 scoping reviews</t>
+          <t>Aguirre, Adams, DeLone &amp; McLean</t>
         </is>
       </c>
     </row>
@@ -1163,16 +1163,16 @@
     <row r="29" ht="38" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  → Policy / framework / theory</t>
+          <t xml:space="preserve">  → Policy / regulatory / framework analyses</t>
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>EU/Estonia EHR Law; NIST 800-37 &amp; 800-53; HIPAA De-id; DeLone &amp; McLean IS</t>
+          <t>Holmgren (2023); Estonia eHealth System (2026); EU/Estonia EHR Law (2016); NIST SP 800-37 (2018); NIST SP 800-53 (2020); HIPAA De-identification (2024)</t>
         </is>
       </c>
     </row>

--- a/prisma/prisma-counts.xlsx
+++ b/prisma/prisma-counts.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRISMA Flow Counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search Strings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inclusion-Exclusion Criteria" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded Full Texts (S2)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Screening Log (template)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PRISMA Flow Counts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Search Strings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inclusion-Exclusion Criteria" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Excluded Full Texts (S2)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Full Screening Log (template)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -147,6 +147,9 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -261,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -375,6 +378,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -740,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -750,477 +754,368 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>PRISMA 2020 Flow Diagram — Record Count Tracker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Study: Determinants of eHealth Systems Adoption: A Systematic Review and Multi-Case Analysis</t>
         </is>
       </c>
     </row>
     <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Date: April 29, 2026  |  Reviewer: Dr. Adams  |  Status: Seed set (formal searches pending)</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Date: July 1, 2026  |  Searches executed: June 4, 2026  |  Status: Executed search — reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>PRISMA Stage</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>n (records)</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>Cumulative</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PRISMA Stage</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>n (records)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Cumulative</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SECTION A — IDENTIFICATION</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>SECTION A — IDENTIFICATION</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="24" t="n"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Records identified — PubMed / MEDLINE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1591</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Executed 2026-06-04; export data/searches/pubmed_results.nbib</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Records identified — PubMed / MEDLINE</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Search: eHealth OR EHR OR HIE AND adoption OR implementation OR barriers (2003–2026)</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Records identified — IEEE Xplore</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>97</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Executed 2026-06-04; export data/searches/ieee_results.csv</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Records identified — Scopus</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Equivalent Scopus syntax search</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Databases not searched — Scopus, Web of Science, CINAHL</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Institutional subscription access unavailable (see S1 §4)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Records identified — Web of Science</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>84</v>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>WoS Core Collection; equivalent syntax</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Supplementary — Google Scholar recall check</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0 unique in-window records beyond database hits</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Records identified — CINAHL</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Nursing/allied health focus terms added</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TOTAL RECORDS IDENTIFIED (pre-deduplication)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1688</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1688</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PubMed 1,591 + IEEE 97</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Records identified — IEEE Xplore</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Technical/engineering eHealth literature</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SECTION B — SCREENING</t>
         </is>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Records identified — Google Scholar</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Supplementary; first 5 pages by relevance</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Duplicate records removed</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1680</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Exact DOI + normalized-title match (conservative); audit in data/screened/00_dedup_audit.md</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Records identified — Hand search (reference lists)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Manual screening of reference lists from retained full texts</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Records after deduplication</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1680</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Unique records proceeding to two-stage title/abstract screening</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Records identified — Expert recommendations</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Sources recommended by domain experts/advisors</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Records excluded — Stage 1 (sensitive T/A screen)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>433</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Off-topic tech (E1=154), wrong outcome (E2=202), setting (E3=2), pub-type (E4=69), pre-2015 window (E6=6)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL RECORDS IDENTIFIED (pre-deduplication)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>424</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>424</v>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Sum of all database and supplementary sources</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Records excluded — Stage 2 (scope refinement)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>698</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Out of organizational/system-level scope: patient/consumer-only (X1=259), single-condition intervention (X2=199), EHR-as-data-source (X3=194), out-of-scope tech (X4=14), pub-type (X5=32)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>SECTION B — SCREENING</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="24" t="n"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Total excluded — title/abstract screening</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1131</v>
+      </c>
+      <c r="C16" t="n">
+        <v>549</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stage 1 (433) + Stage 2 (698)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Duplicate records removed</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>394</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Estimated duplicates removed across overlapping databases (PubMed/Scopus/WoS overlap)</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Reports sought / assessed for eligibility</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>549</v>
+      </c>
+      <c r="C17" t="n">
+        <v>549</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Full text retrieved for 272 (PubMed Central OA); 277 assessed on abstract</t>
         </is>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Records after deduplication</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>394</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>394</v>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Unique records proceeding to title/abstract screening</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reports excluded after eligibility assessment</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>48</v>
+      </c>
+      <c r="C18" t="n">
+        <v>501</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EHR-as-data-source only (41); patient/consumer-only (4); publication type (3). See Supplementary File S2.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Records excluded — title/abstract screening</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>351</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Excluded: not eHealth adoption; wrong language; editorial/commentary; wrong population</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SECTION C — INCLUSION</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Records sought for full-text retrieval</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>43</v>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>Title/abstract inconclusive or promising — full text sought</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Studies included in qualitative synthesis</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>501</v>
+      </c>
+      <c r="C20" t="n">
+        <v>501</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Screened from executed PubMed + IEEE search; U-T-I-O extraction in data/final/included_studies_evidence.csv</t>
         </is>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Full texts not retrievable</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Unable to access after library and interlibrary loan requests</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Studies addressing all four U-T-I-O domains</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>285</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>57% of included studies</t>
         </is>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Full texts assessed for eligibility</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Full texts screened against inclusion/exclusion criteria</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Studies addressing three domains</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Full texts excluded after review</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Excl. reasons: wrong outcome (E2, n=9); insufficient methodology (E4, n=6); wrong setting (E3, n=4); duplicate/better source retained (E5, n=4); wrong focus (E1, n=1). See Supplementary File S2 for full list.</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Systematic/scoping/umbrella reviews</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>54</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Review-type articles within included set</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>SECTION C — INCLUSION</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="24" t="n"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Purposively selected national cases</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ONC HIE (U.S.); NHS Shared Care Records (UK); Estonia eHealth; VA/DoD EHR Modernisation — separate purposive case arm</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="38" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Studies included in qualitative synthesis</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>17 sources: 4 systematic/umbrella reviews; 3 scoping/narrative reviews; 4 government/audit reports; 6 policy/regulatory/framework analyses</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="38" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Systematic / umbrella reviews</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Eden, Kruse, Fennelly, Torab-Miandoab</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Scoping / narrative reviews</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Aguirre, Adams, DeLone &amp; McLean</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Government / institutional reports</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>GAO VA 2025, GAO DoD 2024, ONC 2025, NHS 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Policy / regulatory / framework analyses</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Holmgren (2023); Estonia eHealth System (2026); EU/Estonia EHR Law (2016); NIST SP 800-37 (2018); NIST SP 800-53 (2020); HIPAA De-identification (2024)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Purposively selected national cases</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>ONC HIE (U.S.); NHS Shared Care Records (UK); Estonia eHealth; VA/DoD EHR Modernisation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL SOURCES IN EVIDENCE BASE</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>17 systematic review sources + 4 purposively selected cases</t>
-        </is>
-      </c>
-    </row>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TOTAL EVIDENCE BASE</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>505</v>
+      </c>
+      <c r="C25" t="n">
+        <v>505</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>501 included studies + 4 national cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1"/>
+    <row r="27" ht="38" customHeight="1"/>
+    <row r="28" ht="38" customHeight="1"/>
+    <row r="29" ht="38" customHeight="1"/>
+    <row r="30" ht="38" customHeight="1"/>
+    <row r="31" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
